--- a/Fuentes/Corpus_Equipos (1).xlsx
+++ b/Fuentes/Corpus_Equipos (1).xlsx
@@ -49,7 +49,7 @@
     <t>Christian Rosales</t>
   </si>
   <si>
-    <t>Juan Zavala</t>
+    <t>Coordinación</t>
   </si>
   <si>
     <t>EL-0001</t>
